--- a/tomtest.xlsx
+++ b/tomtest.xlsx
@@ -469,7 +469,7 @@
         <v>46223.5</v>
       </c>
       <c r="F2" s="2">
-        <v>46223.60416666666</v>
+        <v>46223.625</v>
       </c>
       <c r="G2" t="s">
         <v>15</v>
@@ -495,7 +495,7 @@
         <v>46222.375</v>
       </c>
       <c r="F3" s="2">
-        <v>46222.41666666666</v>
+        <v>46222.4375</v>
       </c>
       <c r="G3" t="s">
         <v>15</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
@@ -521,7 +521,7 @@
         <v>46223.5</v>
       </c>
       <c r="F4" s="2">
-        <v>46223.60416666666</v>
+        <v>46223.625</v>
       </c>
       <c r="G4" t="s">
         <v>15</v>
@@ -532,7 +532,7 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
@@ -547,7 +547,7 @@
         <v>46227.64583333334</v>
       </c>
       <c r="F5" s="2">
-        <v>46227.66666666666</v>
+        <v>46227.6875</v>
       </c>
       <c r="G5" t="s">
         <v>16</v>
